--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="40">
   <si>
     <t>玩法配置ID</t>
   </si>
@@ -124,6 +124,21 @@
     <t>0</t>
   </si>
   <si>
+    <t>SP_02</t>
+  </si>
+  <si>
+    <t>Monster_03</t>
+  </si>
+  <si>
+    <t>Boss_01</t>
+  </si>
+  <si>
+    <t>Monster_11</t>
+  </si>
+  <si>
+    <t>PushMap_02</t>
+  </si>
+  <si>
     <t>Monster_04</t>
   </si>
   <si>
@@ -136,16 +151,7 @@
     <t>TZ_01</t>
   </si>
   <si>
-    <t>SP_02</t>
-  </si>
-  <si>
-    <t>Monster_03</t>
-  </si>
-  <si>
-    <t>Monster_11</t>
-  </si>
-  <si>
-    <t>Boss_01</t>
+    <t>PushMap_03</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1120,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.2583333333333" customWidth="1"/>
@@ -1210,7 +1216,7 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -1230,16 +1236,16 @@
         <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -1248,7 +1254,7 @@
         <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1259,19 +1265,19 @@
         <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H6" t="s">
         <v>27</v>
@@ -1279,19 +1285,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>20</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -1305,19 +1311,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -1325,33 +1331,267 @@
       <c r="G8" t="s">
         <v>29</v>
       </c>
-      <c r="H8">
-        <v>2</v>
+      <c r="H8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
       </c>
       <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
         <v>36</v>
       </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15">
+        <v>30</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" t="s">
         <v>29</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16" t="s">
         <v>28</v>
       </c>
-      <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" t="s">
         <v>27</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="41">
   <si>
     <t>玩法配置ID</t>
   </si>
@@ -133,22 +133,25 @@
     <t>Boss_01</t>
   </si>
   <si>
+    <t>Monster_12</t>
+  </si>
+  <si>
+    <t>PushMap_02</t>
+  </si>
+  <si>
+    <t>Monster_04</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>SP_03</t>
+  </si>
+  <si>
+    <t>TZ_01</t>
+  </si>
+  <si>
     <t>Monster_11</t>
-  </si>
-  <si>
-    <t>PushMap_02</t>
-  </si>
-  <si>
-    <t>Monster_04</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>SP_03</t>
-  </si>
-  <si>
-    <t>TZ_01</t>
   </si>
   <si>
     <t>PushMap_03</t>
@@ -771,9 +774,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1215,19 +1221,19 @@
       <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1241,19 +1247,19 @@
       <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
         <v>2</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1267,19 +1273,19 @@
       <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="G6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1293,19 +1299,19 @@
       <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>30</v>
       </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1319,19 +1325,19 @@
       <c r="C8" t="s">
         <v>35</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>30</v>
       </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1345,19 +1351,19 @@
       <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>30</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>2</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1371,19 +1377,19 @@
       <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>20</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>3</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1395,21 +1401,21 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2">
         <v>2</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>3</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>2</v>
       </c>
     </row>
@@ -1421,27 +1427,27 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="G12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
         <v>25</v>
@@ -1449,25 +1455,25 @@
       <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>30</v>
       </c>
-      <c r="E13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="E13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
         <v>25</v>
@@ -1475,25 +1481,25 @@
       <c r="C14" t="s">
         <v>35</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>30</v>
       </c>
-      <c r="E14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
@@ -1501,25 +1507,25 @@
       <c r="C15" t="s">
         <v>26</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>30</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>2</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
@@ -1527,71 +1533,71 @@
       <c r="C16" t="s">
         <v>31</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>20</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>3</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17">
+        <v>39</v>
+      </c>
+      <c r="D17" s="2">
         <v>2</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>3</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="G18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>27</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="43">
   <si>
     <t>玩法配置ID</t>
   </si>
@@ -155,6 +155,12 @@
   </si>
   <si>
     <t>PushMap_03</t>
+  </si>
+  <si>
+    <t>SP_04</t>
+  </si>
+  <si>
+    <t>SP_05</t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1132,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.2583333333333" customWidth="1"/>
@@ -1456,7 +1462,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>27</v>
@@ -1482,7 +1488,7 @@
         <v>35</v>
       </c>
       <c r="D14" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>27</v>
@@ -1508,7 +1514,7 @@
         <v>26</v>
       </c>
       <c r="D15" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E15" s="2">
         <v>2</v>
@@ -1557,7 +1563,7 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -1580,24 +1586,76 @@
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D18" s="2">
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="2">
+        <v>30</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>27</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
@@ -1537,7 +1537,7 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D16" s="2">
         <v>20</v>
@@ -1615,7 +1615,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D19" s="2">
         <v>30</v>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
@@ -1485,7 +1485,7 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2">
         <v>20</v>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="46">
   <si>
     <t>玩法配置ID</t>
   </si>
@@ -58,6 +58,9 @@
     <t>同点出怪顺序</t>
   </si>
   <si>
+    <t>初始朝向</t>
+  </si>
+  <si>
     <t>FK → PushMapGameplayConfig</t>
   </si>
   <si>
@@ -82,6 +85,9 @@
     <t>同 SpawnPointId 多行时升序</t>
   </si>
   <si>
+    <t>0=每怪随机1~8；1正上/2右上/3正右/4右下/5正下/6左下/7正左/8左上；缺省5</t>
+  </si>
+  <si>
     <t>GameplayConfigId</t>
   </si>
   <si>
@@ -104,6 +110,9 @@
   </si>
   <si>
     <t>SpawnOrder</t>
+  </si>
+  <si>
+    <t>InitialFacing</t>
   </si>
   <si>
     <t>PushMap_01</t>
@@ -635,148 +644,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1132,14 +1141,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.2583333333333" customWidth="1"/>
     <col min="3" max="3" width="13.2583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1164,94 +1173,106 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2">
         <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2">
         <v>3</v>
@@ -1260,102 +1281,114 @@
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="D7" s="2">
+        <v>30</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="H7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2">
+        <v>30</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
         <v>29</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="2">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="2">
-        <v>30</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
       </c>
       <c r="D9" s="2">
         <v>30</v>
@@ -1364,24 +1397,27 @@
         <v>2</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>30</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
         <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
       </c>
       <c r="D10" s="2">
         <v>20</v>
@@ -1390,24 +1426,27 @@
         <v>3</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>30</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -1416,102 +1455,114 @@
         <v>3</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H11" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
         <v>29</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
       </c>
       <c r="D13" s="2">
         <v>20</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="C14" t="s">
         <v>29</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
       </c>
       <c r="D14" s="2">
         <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
         <v>29</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
       </c>
       <c r="D15" s="2">
         <v>20</v>
@@ -1520,24 +1571,27 @@
         <v>2</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
         <v>29</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
       </c>
       <c r="D16" s="2">
         <v>20</v>
@@ -1546,24 +1600,27 @@
         <v>3</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>30</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -1572,91 +1629,103 @@
         <v>3</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H17" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D18" s="2">
         <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>26</v>
-      </c>
       <c r="D19" s="2">
         <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
